--- a/Estimates - Option A (Architecture Mapped) v4.xlsx
+++ b/Estimates - Option A (Architecture Mapped) v4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Venkata\JA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D929ECC-A0F7-4408-9A8D-778F13F862B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B81651-F332-424A-932E-B6BD9BF2E566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -630,7 +630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="67.73046875" bestFit="1" customWidth="1"/>
@@ -1103,14 +1103,20 @@
         <v>75</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
         <v>77</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="F36">
+        <f>15000/85</f>
+        <v>176.47058823529412</v>
       </c>
     </row>
   </sheetData>
